--- a/data/trans_orig/IP2906_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31466</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>56371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39489</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75368</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171956</t>
+          <t>171505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208051</t>
+          <t>206428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205397</t>
+          <t>206255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252992</t>
+          <t>254849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>392060</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>450408</t>
+          <t>451243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212633</t>
+          <t>214256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248728</t>
+          <t>249179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249079</t>
+          <t>247222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296674</t>
+          <t>295816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>472347</t>
+          <t>471512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>530695</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>45875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49632</t>
+          <t>49677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72049</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101588</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130494</t>
+          <t>131959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78507</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97705</t>
+          <t>96932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106580</t>
+          <t>106245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128997</t>
+          <t>128952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190941</t>
+          <t>189476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219847</t>
+          <t>221162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245618</t>
+          <t>245440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288835</t>
+          <t>286338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289224</t>
+          <t>290695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>343369</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>542294</t>
+          <t>546326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>616890</t>
+          <t>619637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327523</t>
+          <t>330020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370740</t>
+          <t>370918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>395675</t>
+          <t>396269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449820</t>
+          <t>448349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738513</t>
+          <t>735766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813109</t>
+          <t>809077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2906_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23602</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17452</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30204</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21257</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12927</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29180</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31744</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>33982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>51238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30113</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23511</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36263</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31611</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23688</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39941</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>59,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34060</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>19806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40330</t>
+          <t>31456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>65671</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76210</t>
+          <t>64767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>218407</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>196715</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>239292</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>190614</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>171505</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>206428</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>230710</t>
+          <t>191254</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206255</t>
+          <t>173726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254849</t>
+          <t>207696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>421324</t>
+          <t>409661</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390425</t>
+          <t>379587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451243</t>
+          <t>437721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>244953</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>224068</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>266645</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>230070</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>214256</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>249179</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>271361</t>
+          <t>225568</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247222</t>
+          <t>209126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295816</t>
+          <t>243096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>501431</t>
+          <t>470521</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471512</t>
+          <t>442461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>532330</t>
+          <t>500595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>420684</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>420684</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>420684</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416822</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416822</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>922755</t>
+          <t>880182</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>922755</t>
+          <t>880182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>922755</t>
+          <t>880182</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56439</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45865</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66925</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55033</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45875</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63932</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60547</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72384</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>111978</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100273</t>
+          <t>99306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131959</t>
+          <t>128390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107827</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97341</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>118401</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>87774</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78875</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>96932</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>118082</t>
+          <t>88021</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106245</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128952</t>
+          <t>97140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>205855</t>
+          <t>195849</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189476</t>
+          <t>179437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221162</t>
+          <t>208521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>298448</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>269880</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>323279</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>266905</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>245440</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>286338</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>265810</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290695</t>
+          <t>245778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>287328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>582446</t>
+          <t>564258</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>546326</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>619637</t>
+          <t>597201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>382893</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>358062</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>411461</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>349453</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>330020</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>370918</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>423503</t>
+          <t>339608</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396269</t>
+          <t>318090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>448349</t>
+          <t>359640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>772957</t>
+          <t>722500</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735766</t>
+          <t>689557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>809077</t>
+          <t>754075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>616358</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>616358</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>616358</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605418</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605418</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605418</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1355403</t>
+          <t>1286758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1355403</t>
+          <t>1286758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1355403</t>
+          <t>1286758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
